--- a/zy70797/reports/orphan_report.xlsx
+++ b/zy70797/reports/orphan_report.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="孤儿服务清单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="无效条目" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="统计汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="统计汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,7 +505,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.yaml:5</t>
+          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.csv:6</t>
         </is>
       </c>
     </row>
@@ -544,7 +543,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.yaml:2</t>
+          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.csv:3</t>
         </is>
       </c>
     </row>
@@ -582,7 +581,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.yaml:1</t>
+          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.csv:2</t>
         </is>
       </c>
     </row>
@@ -620,7 +619,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.yaml:4</t>
+          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.csv:5</t>
         </is>
       </c>
     </row>
@@ -650,7 +649,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.yaml:8</t>
+          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.csv:7</t>
         </is>
       </c>
     </row>
@@ -684,7 +683,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.yaml:3</t>
+          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.csv:4</t>
         </is>
       </c>
     </row>
@@ -699,88 +698,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>条目名称</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>解析错误</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>来源位置</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>原始内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>invalid_type_str</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Item must be a dictionary</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.yaml:6</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>this is not a valid service entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>unnamed_service</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>service_name is required</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>/Users/lzy/pro/solo/workspaces/zy70797/examples/service_catalog.yaml:7</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">repository: invalid
-service_name: ''
-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -803,7 +720,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -823,7 +740,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
